--- a/output/2026-09-30_22_Malesia_Johor_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-30_22_Malesia_Johor_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fornitore MRO industriale, oltre 300.000 prodotti incl. saldatura MIG/TIG/ARC; verificato</t>
+          <t>Fornitore MRO industriale, oltre 300.000 prodotti incl. saldatura MIG/TIG/ARC; verificato [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hardware/macchinari industriali, power tools, saldatrici; fondata 2013</t>
+          <t>Hardware/macchinari industriali, power tools, saldatrici; fondata 2013 [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hardware, macchinari, power tools, saldatrici; verificato via WebSearch (WebFetch 503)</t>
+          <t>Hardware, macchinari, power tools, saldatrici; verificato via WebSearch (WebFetch 503) [DUPLICATO — vedi anche: 2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hardware, macchinari, power tools, DPI/sicurezza; dal 1979</t>
+          <t>Hardware, macchinari, power tools, DPI/sicurezza; dal 1979 [DUPLICATO — vedi anche: 2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dealer autorizzato Doosan (DN Solutions): CNC tornio/fresa, macchine usate; verificato via WebSearch</t>
+          <t>Dealer autorizzato Doosan (DN Solutions): CNC tornio/fresa, macchine usate; verificato via WebSearch [DUPLICATO — vedi anche: 2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Macchine utensili nuove/usate (torni, fresatrici CNC, presse); dal 2008</t>
+          <t>Macchine utensili nuove/usate (torni, fresatrici CNC, presse); dal 2008 [DUPLICATO — vedi anche: 2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dealer/importatore macchine utensili CNC, riparazione Fanuc/Mitsubishi/Siemens; dal 1991; verificato via WebSearch</t>
+          <t>Dealer/importatore macchine utensili CNC, riparazione Fanuc/Mitsubishi/Siemens; dal 1991; verificato via WebSearch [DUPLICATO — vedi anche: 2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1119,7 +1119,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>info@penta-ventura.com.my</t>
@@ -1295,7 +1294,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Attrezzature industriali custom, laser cutting, piegatrice/cesoia lamiera; email confermata via ricerca indipendente</t>
+          <t>Attrezzature industriali custom, laser cutting, piegatrice/cesoia lamiera; email confermata via ricerca indipendente [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1337,7 +1336,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dust collector, air pollution control, ventilatori industriali; ISO 9001/45001, dal 2009</t>
+          <t>Dust collector, air pollution control, ventilatori industriali; ISO 9001/45001, dal 2009 [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1379,7 +1378,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dust collector (nativo woodworking, applicabile a metalworking), abrasivi, utensili da taglio (marchio SOUSTA)</t>
+          <t>Dust collector (nativo woodworking, applicabile a metalworking), abrasivi, utensili da taglio (marchio SOUSTA) [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1421,7 +1420,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Filtri e cartucce per dust collector, filtrazione aria/HEPA; gruppo con sedi Singapore/Malaysia/Indonesia, email generale di gruppo</t>
+          <t>Filtri e cartucce per dust collector, filtrazione aria/HEPA; gruppo con sedi Singapore/Malaysia/Indonesia, email generale di gruppo [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1436,7 +1435,6 @@
           <t>Dmag Technical Sdn Bhd</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Skudai, Johor (181A, Jalan Impian Emas 22)</t>
@@ -1459,7 +1457,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dust collector a filtro a maniche (bag filter), air pollution control; nessun sito ufficiale, verificato interamente via WebSearch/directory</t>
+          <t>Dust collector a filtro a maniche (bag filter), air pollution control; nessun sito ufficiale, verificato interamente via WebSearch/directory [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1494,10 +1492,9 @@
           <t>+607-234 2307</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Progettazione/esecuzione impianti dust collector, ACMV, sistemi elettrici; email non presente sul sito, dal 2017</t>
+          <t>Progettazione/esecuzione impianti dust collector, ACMV, sistemi elettrici; email non presente sul sito, dal 2017 [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1539,7 +1536,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>EPC ingegneristico: sistemi meccanici/cleanroom; specializzazione dust collector non esplicitamente confermata sul sito, mantenuta con riserva</t>
+          <t>EPC ingegneristico: sistemi meccanici/cleanroom; specializzazione dust collector non esplicitamente confermata sul sito, mantenuta con riserva [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">

--- a/output/2026-09-30_22_Malesia_Johor_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-30_22_Malesia_Johor_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
